--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F85F36-DC0F-42D1-A698-A42D8355502C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C582A0E-11C3-4F1A-9512-F39E83BEEA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="-14805" windowWidth="14130" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-14250" windowWidth="10245" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>floorCount</t>
   </si>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
@@ -455,10 +455,10 @@
       </c>
       <c r="B2" s="2">
         <f>VLOOKUP(C2,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -500,60 +500,6 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <f>VLOOKUP(C5,reference!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <f>VLOOKUP(C6,reference!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
-        <f>VLOOKUP(C7,reference!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -568,7 +514,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C7</xm:sqref>
+          <xm:sqref>C2:C4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C582A0E-11C3-4F1A-9512-F39E83BEEA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A668EEED-7077-4445-91ED-9715CE7CD1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-14250" windowWidth="10245" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16290" yWindow="-14505" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
   <si>
     <t>floorCount</t>
   </si>
@@ -422,11 +422,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -497,10 +497,136 @@
         <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <f>VLOOKUP(C5,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <f>VLOOKUP(C6,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <f>VLOOKUP(C7,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <f>VLOOKUP(C8,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <f>VLOOKUP(C9,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <f>VLOOKUP(C10,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <f>VLOOKUP(C11,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -514,7 +640,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C4</xm:sqref>
+          <xm:sqref>C2:C11</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A668EEED-7077-4445-91ED-9715CE7CD1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCFAD8F-8201-4FDD-A3D2-4F4C363B0705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16290" yWindow="-14505" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="-13605" windowWidth="16995" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>floorCount</t>
   </si>
@@ -74,6 +74,10 @@
   </si>
   <si>
     <t>spriteSelect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>trapTableID</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -422,17 +426,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -448,8 +453,11 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -466,8 +474,11 @@
       <c r="E2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -484,8 +495,11 @@
       <c r="E3" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -502,8 +516,11 @@
       <c r="E4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -520,8 +537,11 @@
       <c r="E5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -538,8 +558,11 @@
       <c r="E6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -556,8 +579,11 @@
       <c r="E7" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -574,8 +600,11 @@
       <c r="E8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -592,8 +621,11 @@
       <c r="E9" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -610,8 +642,11 @@
       <c r="E10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -627,6 +662,9 @@
       </c>
       <c r="E11" s="2">
         <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
